--- a/data/credit_bond_all_2026-10-26.xlsx
+++ b/data/credit_bond_all_2026-10-26.xlsx
@@ -1433,8 +1433,12 @@
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>103.4</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2.27</t>
@@ -2794,74 +2798,72 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26山东同舟MTN001</t>
+          <t>26拱城08</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102684246.IB</t>
+          <t>284259.SH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3+1</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>11.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.10</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>31.24</v>
+        <v>34.96</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26同舟02</t>
+          <t>26拱城07</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+5.00Y</t>
+          <t>2.92Y+1.00Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.0351</t>
+          <t>1.6457</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/1.9000</t>
+          <t>--/1.6300</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司</t>
+          <t>杭州市拱墅区城市建设发展控股集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C 25.56</t>
+          <t>C 28.69</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2871,7 +2873,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 16:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2881,21 +2883,21 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.86</v>
+        <v>4.02</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2906,23 +2908,23 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元,发行金额上限为15亿元,用于偿还本部及子公司流动资金贷款</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期的公司债券“23拱城03”的本金[23拱城03]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,浙商证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2932,69 +2934,73 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司2026年度第一期中期票据</t>
+          <t>杭州市拱墅区城市建设发展控股集团有限公司2026年面向专业投资者非公开发行公司债券(第八期)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2036-10-27</t>
+          <t>2030-10-28</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP12" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2029-10-28</t>
         </is>
       </c>
       <c r="AV12" s="3" t="inlineStr">
@@ -3017,14 +3023,12 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26拱城08</t>
+          <t>26济控K5</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3034,62 +3038,62 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>284259.SH</t>
+          <t>284357.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3+1</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>34.96</v>
+        <v>44.68</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26拱城07</t>
+          <t>26济控04</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.92Y+1.00Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6457</t>
+          <t>1.8643</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/1.6300</t>
+          <t>--/1.8600</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>杭州市拱墅区城市建设发展控股集团有限公司</t>
+          <t>济南财金投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 28.69</t>
+          <t>B- 40.25</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3099,7 +3103,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-26 16:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3112,18 +3116,16 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="U13" s="4" t="n">
-        <v>4.02</v>
-      </c>
+      <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3134,17 +3136,17 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期的公司债券“23拱城03”的本金[23拱城03]</t>
+          <t>本期债券募集资金在扣除发行费用后,拟全部用于基金出资或置换前期用于基金出资的自有资金</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,浙商证券股份有限公司,财通证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3165,7 +3167,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>杭州市拱墅区城市建设发展控股集团有限公司2026年面向专业投资者非公开发行公司债券(第八期)</t>
+          <t>济南财金投资控股集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3175,7 +3177,7 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2030-10-28</t>
+          <t>2031-10-28</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
@@ -3196,37 +3198,33 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP13" s="3"/>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3236,7 +3234,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3254,7 +3252,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26济控K5</t>
+          <t>26嘉铁K1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3264,7 +3262,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>284357.SH</t>
+          <t>284363.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3273,53 +3271,53 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>44.68</v>
+        <v>35.68</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26济控04</t>
+          <t>26嘉铁01</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.8643</t>
+          <t>1.7697</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/1.8600</t>
+          <t>1.8400/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>济南财金投资控股集团有限公司</t>
+          <t>嘉兴市铁路与轨道交通投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 40.25</t>
+          <t>A 71.25</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3329,7 +3327,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 16:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3342,7 +3340,9 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3359,20 +3359,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z14" s="3"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟全部用于基金出资或置换前期用于基金出资的自有资金</t>
+          <t>本期公司债券募集资金扣除发行费用后,2.80亿元拟用于科技创新领域的基金出资以及置换发行前一年内的用于科技创新领域的基金出资,1.20亿元拟用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3393,7 +3397,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>济南财金投资控股集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
+          <t>嘉兴市铁路与轨道交通投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3424,28 +3428,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP14" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3478,7 +3486,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26嘉铁K1</t>
+          <t>26交子02</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3488,62 +3496,62 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>284363.SH</t>
+          <t>284366.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>35.68</v>
+        <v>24.68</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26嘉铁01</t>
+          <t>26交子01</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>2.46Y+2.00Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7697</t>
+          <t>1.6708</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.8400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市铁路与轨道交通投资集团有限责任公司</t>
+          <t>成都交子公园金融商务区投资开发有限责任公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>A 71.25</t>
+          <t>C+ 34.63</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3553,7 +3561,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-26 16:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3566,43 +3574,37 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="U15" s="4" t="n">
-        <v>5.0</v>
-      </c>
+      <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,2.80亿元拟用于科技创新领域的基金出资以及置换发行前一年内的用于科技创新领域的基金出资,1.20亿元拟用于偿还有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还到期的有息债务[21交子公园MTN001]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3623,7 +3625,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市铁路与轨道交通投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>成都交子公园金融商务区投资开发有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3654,27 +3656,27 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6*无效</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
@@ -3684,7 +3686,7 @@
       </c>
       <c r="AU15" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-28</t>
         </is>
       </c>
       <c r="AV15" s="3" t="inlineStr">
@@ -3694,7 +3696,7 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3712,7 +3714,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26交子02</t>
+          <t>26大唐K1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3722,62 +3724,62 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>284366.SH</t>
+          <t>246333.SH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>20Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>24.68</v>
+        <v>7.13</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26交子01</t>
+          <t>25大唐集MTN002</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.46Y+2.00Y</t>
+          <t>1.32Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6708</t>
+          <t>1.4687</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4500</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>成都交子公园金融商务区投资开发有限责任公司</t>
+          <t>中国大唐集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.63</t>
+          <t>B- 42.05</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3787,7 +3789,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 16:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3800,37 +3802,43 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>2.61</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>2.14%~2.24%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z16" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还到期的有息债务[21交子公园MTN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3841,7 +3849,7 @@
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3851,20 +3859,24 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>成都交子公园金融商务区投资开发有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>中国大唐集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
-        </is>
-      </c>
-      <c r="AK16" s="3"/>
+          <t>2046-10-28</t>
+        </is>
+      </c>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3887,32 +3899,32 @@
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>6*无效</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV16" s="3" t="inlineStr">
@@ -3922,7 +3934,7 @@
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3940,7 +3952,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26大唐K1</t>
+          <t>26青城14</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3950,62 +3962,62 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>246333.SH</t>
+          <t>246326.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>20Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>20.0</v>
+        <v>10.6</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
         <v>2.13</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>7.13</v>
+        <v>49.24</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25大唐集MTN002</t>
+          <t>25青城07</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>1.32Y</t>
+          <t>8.47Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.4687</t>
+          <t>2.0464</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/1.4500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>中国大唐集团有限公司</t>
+          <t>青岛城市建设投资(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 42.05</t>
+          <t>B- 39.18</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4029,17 +4041,17 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.61</v>
+        <v>2.06</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.14%~2.24%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4047,24 +4059,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
+          <t>本期债券发行规模不超过21.20亿元(含21.20亿元)募集资金拟全部用于偿还发行人到期的公司债券本金[23青城10,23青城11]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中信证券股份有限公司,长江证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,中泰证券股份有限公司,中邮证券有限责任公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4075,7 +4083,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4085,7 +4093,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>中国大唐集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>青岛城市建设投资(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4095,14 +4103,10 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2046-10-28</t>
-        </is>
-      </c>
-      <c r="AK17" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2036-10-28</t>
+        </is>
+      </c>
+      <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4125,27 +4129,27 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4178,7 +4182,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26青城14</t>
+          <t>26皖通04(取消发行)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4188,47 +4192,43 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>246326.SH</t>
+          <t>DY246309.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>10.6</v>
+        <v>3.5</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>49.24</v>
-      </c>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25青城07</t>
+          <t>25皖通V2</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>8.47Y</t>
+          <t>3.35Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.0464</t>
+          <t>1.5657</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>青岛城市建设投资(集团)有限责任公司</t>
+          <t>安徽皖通高速公路股份有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 39.18</t>
+          <t>D+ 9.19</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4266,18 +4266,16 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="U18" s="4" t="n">
-        <v>2.06</v>
-      </c>
+      <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4288,17 +4286,17 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过21.20亿元(含21.20亿元)募集资金拟全部用于偿还发行人到期的公司债券本金[23青城10,23青城11]</t>
+          <t>本期债券发行规模不超过7.00亿元(含7.00亿元),本期公司债券募集资金扣除发行费用后,拟将不超过3.00亿元(含3.00亿元)用于固定资产项目投资,拟将不超过3.00亿元(含3.00亿元)用于补充流动资金,拟将不超过1.00亿元(含1.00亿元)用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,长江证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,中泰证券股份有限公司,中邮证券有限责任公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4319,7 +4317,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>青岛城市建设投资(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)</t>
+          <t>安徽皖通高速公路股份有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4329,7 +4327,7 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2036-10-28</t>
+          <t>2031-10-28</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
@@ -4355,27 +4353,27 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4408,7 +4406,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26皖通04(取消发行)</t>
+          <t>26秦发03(取消发行)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4418,7 +4416,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>DY246309.SH</t>
+          <t>DY284282.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4427,102 +4425,102 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>25秦发02</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>3.35Y</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>1.7504</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>1.8000/1.6800</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>秦皇岛城市发展投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.69</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>10-26 15:00</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>25皖通V2</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>3.35Y</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>1.5657</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>安徽皖通高速公路股份有限公司</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>D+ 9.19</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>10-26 16:00</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>河北省-秦皇岛市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过7.00亿元(含7.00亿元),本期公司债券募集资金扣除发行费用后,拟将不超过3.00亿元(含3.00亿元)用于固定资产项目投资,拟将不超过3.00亿元(含3.00亿元)用于补充流动资金,拟将不超过1.00亿元(含1.00亿元)用于偿还有息债务。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[24秦发03]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>财达证券股份有限公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4543,17 +4541,17 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>安徽皖通高速公路股份有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)(取消发行)</t>
+          <t>秦皇岛城市发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
@@ -4564,42 +4562,42 @@
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4632,7 +4630,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26秦发03(取消发行)</t>
+          <t>26启东F2</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4642,7 +4640,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>DY284282.SH</t>
+          <t>284355.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -4651,49 +4649,53 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.5</v>
+        <v>15.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>37.68</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>25秦发02</t>
+          <t>26启东F1</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3.35Y</t>
+          <t>4.36Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.7504</t>
+          <t>1.7568</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.6800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>秦皇岛城市发展投资控股集团有限公司</t>
+          <t>启东城投集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.69</t>
+          <t>C- 15.39</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4703,7 +4705,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 16:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4713,19 +4715,19 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4736,17 +4738,17 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>河北省-秦皇岛市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[24秦发03]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金[23启东02]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>财达证券股份有限公司,浙商证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,东方证券股份有限公司,中国银河证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4767,7 +4769,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>秦皇岛城市发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)(取消发行)</t>
+          <t>启东城投集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4777,7 +4779,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2031-10-28</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4793,37 +4795,37 @@
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4856,7 +4858,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26启东F2</t>
+          <t>26泰投01</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4866,7 +4868,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>284355.SH</t>
+          <t>284390.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4875,38 +4877,38 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>15.0</v>
+        <v>17.7</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>37.68</v>
+        <v>53.68</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26启东F1</t>
+          <t>26泰兴城投PPN004</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>4.36Y</t>
+          <t>2.77Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7568</t>
+          <t>1.6655</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4916,12 +4918,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>启东城投集团有限公司</t>
+          <t>泰兴市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 15.39</t>
+          <t>C- 10.43</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4931,7 +4933,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-26 16:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4948,12 +4950,12 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4964,17 +4966,17 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金[23启东02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,仅用于偿还“23泰投01”和“24泰投01”到期的公司债券本金。[23泰投01,24泰投01]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,东方证券股份有限公司,中国银河证券股份有限公司,国金证券股份有限公司</t>
+          <t>东吴证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -4995,7 +4997,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>启东城投集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>泰兴市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5031,22 +5033,22 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
@@ -5084,72 +5086,74 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26泰投01</t>
+          <t>26首创生态SCP005</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>284390.SH</t>
+          <t>012682544.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.26 ~ 1.46</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>53.68</v>
+        <v>19.36</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26泰兴城投PPN004</t>
+          <t>26首创生态SCP004</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.77Y</t>
+          <t>143D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6655</t>
+          <t>1.4445</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>泰兴市城市投资发展集团有限公司</t>
+          <t>北京首创生态环保集团股份有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 10.43</t>
+          <t>B- 40.54</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5159,7 +5163,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 11:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5169,46 +5173,48 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="U22" s="3"/>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>1.31</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,仅用于偿还“23泰投01”和“24泰投01”到期的公司债券本金。[23泰投01,24泰投01]</t>
+          <t>发行人本期超短期融资券拟募集资金10亿元，全部用于偿还公司本部债务融资工具本金部分[26首创生态SCP001,26首创生态SCP002]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5218,68 +5224,68 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>泰兴市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>北京首创生态环保集团股份有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
+          <t>2027-07-23</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5312,7 +5318,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26首创生态SCP005</t>
+          <t>26珠城轨MTN005</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5322,12 +5328,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>012682544.IB</t>
+          <t>102684253.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -5338,48 +5344,48 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.46</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>19.36</v>
+        <v>24.68</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26首创生态SCP004</t>
+          <t>26珠城轨MTN001</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>143D</t>
+          <t>4.51Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.4445</t>
+          <t>1.6770</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.4700/--</t>
+          <t>1.7000/1.6600</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>北京首创生态环保集团股份有限公司</t>
+          <t>广东珠三角城际轨道交通有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B- 40.54</t>
+          <t>B- 45.83</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5389,12 +5395,12 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-26 11:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5403,17 +5409,19 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V23" s="3"/>
+        <v>4.03</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.51</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5421,26 +5429,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z23" s="3"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券拟募集资金10亿元，全部用于偿还公司本部债务融资工具本金部分[26首创生态SCP001,26首创生态SCP002]</t>
+          <t>本期发行规模人民币10亿元,全部用于偿还发行人本部有息负债</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5455,7 +5467,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>北京首创生态环保集团股份有限公司2026年度第五期超短期融资券</t>
+          <t>广东珠三角城际轨道交通有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5465,7 +5477,7 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2027-07-23</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5486,7 +5498,7 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
@@ -5496,22 +5508,22 @@
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5544,7 +5556,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26珠城轨MTN005</t>
+          <t>26南电MTN009</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5554,19 +5566,19 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102684253.IB</t>
+          <t>102684256.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>4.99Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.0</v>
+        <v>35.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.0</v>
+        <v>35.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -5574,44 +5586,44 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>24.68</v>
+        <v>21.68</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26珠城轨MTN001</t>
+          <t>26南电GN008(科创债)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>4.51Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.6770</t>
+          <t>1.6255</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.7000/1.6600</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>广东珠三角城际轨道交通有限公司</t>
+          <t>中国南方电网有限责任公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 45.83</t>
+          <t>C+ 34.80</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5626,7 +5638,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5634,15 +5646,13 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="U24" s="4" t="n">
-        <v>4.03</v>
-      </c>
+      <c r="U24" s="3"/>
       <c r="V24" s="4" t="n">
-        <v>1.51</v>
+        <v>1.0</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
@@ -5655,24 +5665,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期发行规模人民币10亿元,全部用于偿还发行人本部有息负债</t>
+          <t>本期中期票据拟发行金额35亿元，募集资金拟用于补充发行人及下属单位营运资金</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5683,7 +5689,7 @@
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5693,7 +5699,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>广东珠三角城际轨道交通有限公司2026年度第五期中期票据</t>
+          <t>中国南方电网有限责任公司2026年度第九期中期票据</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5703,7 +5709,7 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2031-10-21</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
@@ -5724,32 +5730,32 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5782,7 +5788,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26南电MTN009</t>
+          <t>26攀枝城建MTN001</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5792,64 +5798,64 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102684256.IB</t>
+          <t>102684245.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>4.99Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>35.0</v>
+        <v>2.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>35.0</v>
+        <v>2.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.57</v>
+        <v>2.0</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>21.68</v>
+        <v>64.68</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26南电GN008(科创债)</t>
+          <t>24攀枝城建MTN001</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>298D</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.6255</t>
+          <t>1.6151</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司</t>
+          <t>攀枝花城建交通(集团)有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.80</t>
+          <t>D- 2.21</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5864,7 +5870,7 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -5872,39 +5878,41 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="U25" s="3"/>
+      <c r="U25" s="4" t="n">
+        <v>4.7</v>
+      </c>
       <c r="V25" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-攀枝花市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行金额35亿元，募集资金拟用于补充发行人及下属单位营运资金</t>
+          <t>本期中期票据发行金额2.00亿元,根据发行人资金需求状况,拟将2.00亿元募集资金用于偿还存量债务融资工具[21攀枝城投MTN001]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5915,7 +5923,7 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5925,7 +5933,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司2026年度第九期中期票据</t>
+          <t>攀枝花城建交通(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5935,7 +5943,7 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-10-21</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -5946,7 +5954,7 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
@@ -5956,32 +5964,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6014,7 +6022,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26攀枝城建MTN001</t>
+          <t>26苏元禾MTN003B(科创债)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6024,7 +6032,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>102684245.IB</t>
+          <t>102684249.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -6033,55 +6041,55 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.0</v>
+        <v>1.59</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>64.68</v>
+        <v>23.68</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24攀枝城建MTN001</t>
+          <t>26苏元禾MTN002B(科创债)</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>298D</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.6151</t>
+          <t>1.6890</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/1.6850</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>攀枝花城建交通(集团)有限公司</t>
+          <t>苏州元禾控股股份有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D- 2.21</t>
+          <t>C 26.62</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6096,7 +6104,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -6105,40 +6113,40 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.7</v>
+        <v>3.12</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>四川省-攀枝花市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额2.00亿元,根据发行人资金需求状况,拟将2.00亿元募集资金用于偿还存量债务融资工具[21攀枝城投MTN001]</t>
+          <t>本期债务融资工具发行拟募集资金10亿元,全部用于置换发行人一年以内用于科技创新领域基金出资的自有资金投入。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6159,7 +6167,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>攀枝花城建交通(集团)有限公司2026年度第一期中期票据</t>
+          <t>苏州元禾控股股份有限公司2026年度第三期科技创新债券(品种二)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6180,7 +6188,7 @@
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
@@ -6190,32 +6198,28 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP26" s="3"/>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6248,7 +6252,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26苏元禾MTN003B(科创债)</t>
+          <t>26杭州联合农商小微债01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6258,64 +6262,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>102684249.IB</t>
+          <t>212680078.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>23.68</v>
+        <v>29.17</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26苏元禾MTN002B(科创债)</t>
+          <t>25杭州联合农商小微债01</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>2.04Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6890</t>
+          <t>1.4816</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.6850</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>苏州元禾控股股份有限公司</t>
+          <t>杭州联合农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C 26.62</t>
+          <t>C 27.68</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6330,28 +6334,26 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>4.77</v>
+      </c>
+      <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.50%~1.60%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6359,31 +6361,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z27" s="3"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行拟募集资金10亿元,全部用于置换发行人一年以内用于科技创新领域基金出资的自有资金投入。</t>
+          <t>本期债券募集资金将全部用于发放小型微型企业贷款。</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,中国银行股份有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,首创证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
@@ -6393,7 +6399,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>苏州元禾控股股份有限公司2026年度第三期科技创新债券(品种二)</t>
+          <t>杭州联合农村商业银行股份有限公司2026年小型微型企业贷款专项金融债券</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6403,49 +6409,57 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2029-10-28</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="AM27" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>金融</t>
         </is>
       </c>
-      <c r="AP27" s="3"/>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6478,7 +6492,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26杭州联合农商小微债01</t>
+          <t>26融和融资MTN004</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6488,7 +6502,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>212680078.IB</t>
+          <t>102684262.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -6497,55 +6511,55 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.41 ~ 1.61</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>29.17</v>
+        <v>25.17</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25杭州联合农商小微债01</t>
+          <t>24融和05</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.04Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.4816</t>
+          <t>1.6057</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>杭州联合农村商业银行股份有限公司</t>
+          <t>中电投融和融资租赁有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C 27.68</t>
+          <t>C- 19.66</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6560,26 +6574,28 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="V28" s="3"/>
+        <v>1.34</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.60%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6587,35 +6603,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将全部用于发放小型微型企业贷款。</t>
+          <t>本期债务融资工具发行金额5亿元,拟全部用于归还发行人即将到期的债务融资工具[23融和融资MTN006(碳中和债)]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,中国银行股份有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,首创证券股份有限公司</t>
+          <t>中信银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -6625,7 +6637,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>杭州联合农村商业银行股份有限公司2026年小型微型企业贷款专项金融债券</t>
+          <t>中电投融和融资租赁有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6635,64 +6647,64 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
+          <t>2029-10-27</t>
         </is>
       </c>
       <c r="AK28" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AO28" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ28" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR28" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>农商行</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6713,12 +6725,14 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ28" s="3"/>
+      <c r="AZ28" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26融和融资MTN004</t>
+          <t>26浙交投SCP015</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6728,64 +6742,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>102684262.IB</t>
+          <t>012682541.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.41 ~ 1.61</t>
+          <t>1.20 ~ 1.55</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>25.17</v>
+        <v>19.36</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>24融和05</t>
+          <t>26浙交投SCP013</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>263D</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6057</t>
+          <t>1.4394</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>1.4400/1.4350</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>中电投融和融资租赁有限公司</t>
+          <t>浙江省交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 19.66</t>
+          <t>B- 35.82</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6795,12 +6809,12 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 14:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -6809,19 +6823,19 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.34</v>
+        <v>2.76</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.1</v>
+        <v>1.0</v>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.38%~1.42%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6832,28 +6846,28 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额5亿元,拟全部用于归还发行人即将到期的债务融资工具[23融和融资MTN006(碳中和债)]</t>
+          <t>本期超短期融资券募集资金10亿元将全部用于偿还发行人和下属子公司有息债务本息</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,交通银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -6863,7 +6877,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>中电投融和融资租赁有限公司2026年度第四期中期票据</t>
+          <t>浙江省交通投资集团有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6873,14 +6887,10 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2029-10-27</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-23</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -6898,32 +6908,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6951,14 +6961,12 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ29" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ29" s="3"/>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26浙交投SCP015</t>
+          <t>26南航集MTN001</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6968,64 +6976,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>012682541.IB</t>
+          <t>102684261.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.55</t>
+          <t>1.41 ~ 1.71</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.36</v>
+        <v>20.17</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26浙交投SCP013</t>
+          <t>25南航集MTN005</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>263D</t>
+          <t>1.99Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.4394</t>
+          <t>1.5184</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.4400/1.4350</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>浙江省交通投资集团有限公司</t>
+          <t>中国南方航空集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 35.82</t>
+          <t>C+ 31.39</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7035,12 +7043,12 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-26 14:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -7049,19 +7057,19 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.0</v>
+        <v>1.06</v>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.38%~1.42%</t>
+          <t>1.51%~1.61%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7072,28 +7080,28 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金10亿元将全部用于偿还发行人和下属子公司有息债务本息</t>
+          <t>本期债务融资工具发行金额为5亿元，发行人计划将用于偿还存量有息债务</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
@@ -7103,7 +7111,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>浙江省交通投资集团有限公司2026年度第十五期超短期融资券</t>
+          <t>中国南方航空集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7113,10 +7121,14 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2027-07-23</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2029-10-27</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -7134,32 +7146,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7187,12 +7199,14 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ30" s="3"/>
+      <c r="AZ30" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26南航集MTN001</t>
+          <t>26中建三局SCP003</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7202,64 +7216,64 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>102684261.IB</t>
+          <t>012682540.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.41 ~ 1.71</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>20.17</v>
+        <v>19.36</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25南航集MTN005</t>
+          <t>24中建三局MTN001</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1.99Y</t>
+          <t>291D+N</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.5184</t>
+          <t>1.5289</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>中国南方航空集团有限公司</t>
+          <t>中建三局集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.39</t>
+          <t>C- 23.94</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7269,12 +7283,12 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 14:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -7283,19 +7297,19 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.44</v>
+        <v>3.0333</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.61%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7306,28 +7320,28 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额为5亿元，发行人计划将用于偿还存量有息债务</t>
+          <t>发行人本期发行超短期融资券15亿元,用于偿还存量债务融资工具[26中建三局SCP001]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -7337,7 +7351,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>中国南方航空集团有限公司2026年度第一期中期票据</t>
+          <t>中建三局集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7347,14 +7361,10 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-10-27</t>
-        </is>
-      </c>
-      <c r="AK31" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-23</t>
+        </is>
+      </c>
+      <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -7377,27 +7387,27 @@
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7425,14 +7435,12 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ31" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ31" s="3"/>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26中建三局SCP003</t>
+          <t>26潞安MTN009A</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7442,64 +7450,64 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>012682540.IB</t>
+          <t>102684250.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>19.36</v>
+        <v>41.17</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>24中建三局MTN001</t>
+          <t>24潞安MTN003</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>291D+N</t>
+          <t>2.56Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.5289</t>
+          <t>1.6128</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>中建三局集团有限公司</t>
+          <t>山西潞安矿业(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 23.94</t>
+          <t>B- 40.43</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7509,12 +7517,12 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>10-26 14:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -7523,19 +7531,19 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.03</v>
+        <v>3.9</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7546,28 +7554,28 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>山西省-长治市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券15亿元,用于偿还存量债务融资工具[26中建三局SCP001]</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币8亿元，募集资金拟用于偿还发行人或下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,广发银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7577,7 +7585,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>中建三局集团有限公司2026年度第三期超短期融资券</t>
+          <t>山西潞安矿业(集团)有限责任公司2026年度第九期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7587,10 +7595,14 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2027-07-23</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2029-10-27</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -7613,27 +7625,27 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7648,7 +7660,7 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7666,74 +7678,74 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26潞安MTN009A</t>
+          <t>26璞信K2</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102684250.IB</t>
+          <t>520543.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
         <v>4.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>41.17</v>
+        <v>47.68</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>24潞安MTN003</t>
+          <t>26璞信K1</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.56Y</t>
+          <t>2.67Y+2.00Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.6128</t>
+          <t>1.9008</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>山西潞安矿业(集团)有限责任公司</t>
+          <t>四川璞信产融投资有限责任公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 40.43</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7743,12 +7755,12 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -7757,46 +7769,44 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>1.25</v>
-      </c>
+        <v>2.73</v>
+      </c>
+      <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>山西省-长治市</t>
+          <t>四川省-泸州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币8亿元，募集资金拟用于偿还发行人或下属子公司的有息负债。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于置换发行前12个月内的科技创新领域相关投资支出</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,兴业银行股份有限公司</t>
+          <t>国信证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7806,79 +7816,71 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>山西潞安矿业(集团)有限责任公司2026年度第九期中期票据(品种一)</t>
+          <t>四川璞信产融投资有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
+          <t>2031-10-27</t>
+        </is>
+      </c>
+      <c r="AK33" s="3"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP33" s="3"/>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t>2029-10-27</t>
         </is>
       </c>
-      <c r="AK33" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="AL33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7886,7 +7888,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7904,59 +7906,59 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26璞信K2</t>
+          <t>26电投融和SCP002</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>520543.SZ</t>
+          <t>012682547.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.32 ~ 1.47</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>47.68</v>
+        <v>18.5</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26璞信K1</t>
+          <t>23电投融和MTN001(碳中和)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.67Y+2.00Y</t>
+          <t>34D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.9008</t>
+          <t>1.4211</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7966,12 +7968,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>四川璞信产融投资有限责任公司</t>
+          <t>电投融和新能源发展有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 28.91</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7981,7 +7983,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7995,75 +7997,77 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="V34" s="3"/>
+        <v>1.1</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>四川省-泸州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于置换发行前12个月内的科技创新领域相关投资支出</t>
+          <t>本期超短期融资券发行金额10亿元,拟全部用于偿还26电投融和SCP001的本金[26电投融和SCP001]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>四川璞信产融投资有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
+          <t>电投融和新能源发展有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2027-04-23</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8099,12 +8103,12 @@
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
         <is>
-          <t>2029-10-27</t>
+          <t/>
         </is>
       </c>
       <c r="AV34" s="3" t="inlineStr">
@@ -8114,7 +8118,7 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
@@ -8132,7 +8136,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26电投融和SCP002</t>
+          <t>26潞安MTN009B</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8142,64 +8146,64 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>012682547.IB</t>
+          <t>102684251.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.32 ~ 1.47</t>
+          <t>1.70 ~ 2.20</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>18.5</v>
+        <v>51.68</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>23电投融和MTN001(碳中和)</t>
+          <t>26潞安MTN008</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>34D</t>
+          <t>4.91Y+N</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.4211</t>
+          <t>1.8764</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8800/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>电投融和新能源发展有限公司</t>
+          <t>山西潞安矿业(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C 28.91</t>
+          <t>B- 40.43</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8214,7 +8218,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -8223,19 +8227,19 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>1.0</v>
+        <v>3.83</v>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8246,28 +8250,28 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山西省-长治市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额10亿元,拟全部用于偿还26电投融和SCP001的本金[26电投融和SCP001]</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币8亿元，募集资金拟用于偿还发行人或下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -8277,7 +8281,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>电投融和新能源发展有限公司2026年度第二期超短期融资券</t>
+          <t>山西潞安矿业(集团)有限责任公司2026年度第九期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8287,7 +8291,7 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2027-04-23</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
@@ -8308,28 +8312,32 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP35" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8344,7 +8352,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8362,7 +8370,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26潞安MTN009B</t>
+          <t>26中远海发MTN006</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8372,64 +8380,64 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102684251.IB</t>
+          <t>102684265.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>4.0</v>
+        <v>30.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
+          <t>1.95 ~ 2.25</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>51.68</v>
+        <v>18.13</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26潞安MTN008</t>
+          <t>25远发K2</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>4.91Y+N</t>
+          <t>13.58Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.8764</t>
+          <t>2.0673</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.8800/--</t>
+          <t>2.0600/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>山西潞安矿业(集团)有限责任公司</t>
+          <t>中远海运发展股份有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 40.43</t>
+          <t>B- 48.55</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8444,7 +8452,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -8453,19 +8461,19 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>2.56</v>
+        <v>2.3767</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>3.83</v>
+        <v>1.34</v>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8473,20 +8481,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z36" s="3"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>山西省-长治市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币8亿元，募集资金拟用于偿还发行人或下属子公司的有息负债。</t>
+          <t>本期募集资金30亿元,拟用于偿还公司本部及合并范围内子公司的有息债务及生产经营活动。</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,兴业银行股份有限公司</t>
+          <t>交通银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8497,7 +8509,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -8507,7 +8519,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>山西潞安矿业(集团)有限责任公司2026年度第九期中期票据(品种二)</t>
+          <t>中远海运发展股份有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8517,10 +8529,14 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
-        </is>
-      </c>
-      <c r="AK36" s="3"/>
+          <t>2041-10-27</t>
+        </is>
+      </c>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -8543,27 +8559,27 @@
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8578,7 +8594,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8596,7 +8612,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26中远海发MTN006</t>
+          <t>26湖南钢铁SCP003</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8606,64 +8622,64 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>102684265.IB</t>
+          <t>012682543.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>15Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.95 ~ 2.25</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2.09</v>
+        <v>1.35</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>18.13</v>
+        <v>19.36</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25远发K2</t>
+          <t>22湖南钢铁GN003(科创票据)</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>13.58Y</t>
+          <t>289D</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2.0673</t>
+          <t>1.4616</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2.0600/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>中远海运发展股份有限公司</t>
+          <t>湖南钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B- 48.55</t>
+          <t>C- 21.00</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8678,7 +8694,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -8687,19 +8703,19 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>2.3767</v>
+        <v>3.34</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8707,35 +8723,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期募集资金30亿元,拟用于偿还公司本部及合并范围内子公司的有息债务及生产经营活动。</t>
+          <t>发行人本次拟发行短期融资券5亿元,募集资金拟全部用于偿还存量有息负债[26湖南钢铁SCP001]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,长沙银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8745,7 +8757,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>中远海运发展股份有限公司2026年度第六期中期票据</t>
+          <t>湖南钢铁集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8755,12 +8767,12 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2041-10-27</t>
+          <t>2027-07-24</t>
         </is>
       </c>
       <c r="AK37" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL37" s="3" t="inlineStr">
@@ -8790,22 +8802,22 @@
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8833,12 +8845,14 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26水发集团MTN005</t>
+          <t>26夏商SCP032</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8848,64 +8862,64 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>102684257.IB</t>
+          <t>012682545.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>0.14Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 2.45</t>
+          <t>1.20 ~ 1.39</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2.05</v>
+        <v>1.39</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>80.72</v>
+        <v>37.29</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25水发集团MTN015</t>
+          <t>26夏商SCP028</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.06Y+N</t>
+          <t>54D</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2.0496</t>
+          <t>1.4293</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>2.1000/--</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>水发集团有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C 29.97</t>
+          <t>B- 41.38</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8920,7 +8934,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -8929,48 +8943,44 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>1.77</v>
+        <v>0.44</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.41%~1.45%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据采取发行金额动态调整机制,基础发行规模人民币0亿元,发行金额上限人民币7亿元,计划用于偿还发行人及子公司的到期有息债务</t>
+          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于偿还发行人即将到期的债务融资工具。[26夏商SCP022]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,长城证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8985,7 +8995,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>水发集团有限公司2026年度第五期中期票据</t>
+          <t>厦门夏商集团有限公司2026年度第三十二期超短期融资券</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8995,7 +9005,7 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2028-10-27</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
@@ -9016,32 +9026,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9056,12 +9066,12 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY38" s="3" t="inlineStr">
@@ -9070,13 +9080,13 @@
         </is>
       </c>
       <c r="AZ38" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26江宁经开MTN007</t>
+          <t>26隧道股份SCP007</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9086,64 +9096,64 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>102684260.IB</t>
+          <t>012682542.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.37Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>31.68</v>
+        <v>14.5</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26江宁经开MTN006</t>
+          <t>26隧道股份SCP006</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.97Y</t>
+          <t>82D</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.7305</t>
+          <t>1.4572</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.9000/1.6800</t>
+          <t>1.5500/1.4200</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>南京江宁经济技术开发集团有限公司</t>
+          <t>上海隧道工程股份有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C 26.16</t>
+          <t>C+ 34.60</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9167,17 +9177,19 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="V39" s="3"/>
+        <v>1.58</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.41%~1.45%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9188,23 +9200,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额5.00亿元,拟用于偿还发行人即将到期的债务融资工具本金[23江宁经开PPN003]</t>
+          <t>本期超短期融资券发行规模为10亿元,募集资金用于补充流动资金、偿还有息负债及置换到期债券等符合要求的用途。</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,上海农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9219,7 +9231,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>南京江宁经济技术开发集团有限公司2026年度第七期中期票据</t>
+          <t>上海隧道工程股份有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9229,7 +9241,7 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
@@ -9250,27 +9262,27 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
@@ -9308,22 +9320,22 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26湖南钢铁SCP003</t>
+          <t>26科建02</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>012682543.IB</t>
+          <t>246323.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -9334,48 +9346,48 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>19.36</v>
+        <v>40.68</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>22湖南钢铁GN003(科创票据)</t>
+          <t>26渝科学城MTN002A</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>289D</t>
+          <t>4.62Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.4616</t>
+          <t>1.7550</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.4700/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>湖南钢铁集团有限公司</t>
+          <t>重庆科学城城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 21.00</t>
+          <t>C- 16.18</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9385,12 +9397,12 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -9399,46 +9411,48 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>1.44</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>重庆市-重庆高新技术产业开发区</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行短期融资券5亿元,募集资金拟全部用于偿还存量有息负债[26湖南钢铁SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人回售公司债券本金[23科建02]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,长沙银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD40" s="3"/>
+          <t>中国国际金融股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr">
+        <is>
+          <t>重庆高新开发建设投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9448,12 +9462,12 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>湖南钢铁集团有限公司2026年度第三期超短期融资券</t>
+          <t>重庆科学城城市建设集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9463,17 +9477,13 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2027-07-24</t>
-        </is>
-      </c>
-      <c r="AK40" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-27</t>
+        </is>
+      </c>
+      <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9488,32 +9498,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9523,7 +9533,7 @@
       </c>
       <c r="AV40" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW40" s="3" t="inlineStr">
@@ -9541,14 +9551,12 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ40" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ40" s="3"/>
     </row>
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP032</t>
+          <t>26贵州能源MTN001(可持续挂钩)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9558,64 +9566,64 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>012682545.IB</t>
+          <t>102690086.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>0.14Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.39</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.39</v>
+        <v>2.0</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>37.29</v>
+        <v>64.68</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP028</t>
+          <t>24贵州能源MTN002</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>54D</t>
+          <t>333D</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.4293</t>
+          <t>1.8038</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/1.4700</t>
+          <t>1.8300/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>贵州能源集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 41.38</t>
+          <t>D+ 8.77</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9625,7 +9633,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>10-26 14:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9639,44 +9647,44 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.44</v>
+        <v>2.0</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.41%~1.45%</t>
+          <t>2.53%~2.63%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于偿还发行人即将到期的债务融资工具。[26夏商SCP022]</t>
+          <t>本期中期票据发行金额不超过10亿元,募集资金将全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,兴业证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9691,7 +9699,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第三十二期超短期融资券</t>
+          <t>贵州能源集团有限公司2026年度第一期中期票据(可持续挂钩)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9701,7 +9709,7 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9732,22 +9740,22 @@
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>煤炭采掘</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9776,80 +9784,80 @@
         </is>
       </c>
       <c r="AZ41" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26隧道股份SCP007</t>
+          <t>26鄂都投05</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>012682542.IB</t>
+          <t>520539.SZ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>0.37Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>14.5</v>
+        <v>44.68</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26隧道股份SCP006</t>
+          <t>26鄂交通04</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>82D</t>
+          <t>4.72Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.4572</t>
+          <t>1.8678</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.5500/1.4200</t>
+          <t>1.8500/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>上海隧道工程股份有限公司</t>
+          <t>湖北交投武汉都市圈投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.60</t>
+          <t>C- 22.14</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9859,7 +9867,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9873,46 +9881,44 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.4667</v>
+      </c>
+      <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.41%~1.45%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为10亿元,募集资金用于补充流动资金、偿还有息负债及置换到期债券等符合要求的用途。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不超过3亿元募集资金用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,上海农村商业银行股份有限公司</t>
+          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9922,33 +9928,33 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>上海隧道工程股份有限公司2026年度第七期超短期融资券</t>
+          <t>湖北交投武汉都市圈投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2027-03-12</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN42" s="3" t="inlineStr">
@@ -9963,22 +9969,22 @@
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
@@ -10016,7 +10022,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26科建02</t>
+          <t>26西影K1</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10026,49 +10032,49 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>246323.SH</t>
+          <t>520541.SZ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>5.0</v>
+        <v>2.6</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5.0</v>
+        <v>2.6</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.50</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>40.68</v>
+        <v>54.68</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26渝科学城MTN002A</t>
+          <t>26西影01</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>4.62Y</t>
+          <t>2.36Y+2.00Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.7550</t>
+          <t>1.9791</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -10078,12 +10084,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>重庆科学城城市建设集团有限公司</t>
+          <t>西部电影集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 16.18</t>
+          <t>C- 22.64</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10107,43 +10113,47 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>2.4</v>
+        <v>3.3154</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z43" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>重庆市-重庆高新技术产业开发区</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人回售公司债券本金[23科建02]</t>
+          <t>本期债券发行总额为不超过2.60亿元(含2.60亿元),本期债券募集资金扣除发行费用后,拟全部用于偿还西影制片厂和西影数码名下有息债务</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>华龙证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3" t="inlineStr">
         <is>
-          <t>重庆高新开发建设投资集团有限公司</t>
+          <t>陕西信用增进投资股份有限公司</t>
         </is>
       </c>
       <c r="AE43" s="3" t="inlineStr">
@@ -10158,17 +10168,17 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>重庆科学城城市建设集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>西部电影集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
@@ -10184,7 +10194,7 @@
       </c>
       <c r="AM43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN43" s="3" t="inlineStr">
@@ -10194,37 +10204,37 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>传媒</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-27</t>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
@@ -10234,7 +10244,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -10252,74 +10262,74 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26贵州能源MTN001(可持续挂钩)</t>
+          <t>26厦贸Y5</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>102690086.IB</t>
+          <t>246327.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1+N</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 2.00</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2.0</v>
+        <v>1.57</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>64.68</v>
+        <v>38.96</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>24贵州能源MTN002</t>
+          <t>厦贸KY1</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>333D</t>
+          <t>359D+N</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.8038</t>
+          <t>1.6115</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>1.8300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>贵州能源集团有限公司</t>
+          <t>厦门国贸集团股份有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.77</t>
+          <t>C 28.25</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10329,7 +10339,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 16:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10343,17 +10353,17 @@
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>2.0</v>
+        <v>2.17</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>2.53%~2.63%</t>
+          <t>1.73%~1.77%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10364,23 +10374,23 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额不超过10亿元,募集资金将全部用于偿还有息债务</t>
+          <t>本期债券发行规模不超过13亿元（含13亿元），本期债券募集资金扣除发行费用后，拟全部用于向“一带一路”沿线国家（地区）采购业务的营运资金支出，或用于置换3个月内上述相关款项</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,世纪证券有限责任公司,中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -10390,12 +10400,12 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>贵州能源集团有限公司2026年度第一期中期票据(可持续挂钩)</t>
+          <t>厦门国贸集团股份有限公司2026年面向专业投资者公开发行"一带一路"可续期公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10405,18 +10415,18 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2027-10-27</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN44" s="3" t="inlineStr">
@@ -10436,22 +10446,22 @@
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>煤炭采掘</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10466,7 +10476,7 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10479,81 +10489,79 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ44" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ44" s="3"/>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26鄂都投05</t>
+          <t>26滁州同创PPN003</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>520539.SZ</t>
+          <t>032680602.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>44.68</v>
+        <v>42.17</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26鄂交通04</t>
+          <t>26滁州同创PPN002</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>4.72Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.8678</t>
+          <t>1.7266</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>1.8500/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>湖北交投武汉都市圈投资发展集团有限公司</t>
+          <t>滁州市同创建设投资有限责任公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 22.14</t>
+          <t>C- 19.99</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10563,12 +10571,12 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -10577,17 +10585,19 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>3.4667</v>
-      </c>
-      <c r="V45" s="3"/>
+        <v>5.44</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10598,23 +10608,23 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>安徽省-滁州市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不超过3亿元募集资金用于偿还有息债务。</t>
+          <t>首期发行金额为5亿元,计划将募集资金用于偿还债务融资工具本金[25滁州同创CP003,25滁州同创CP004]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>徽商银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10624,12 +10634,12 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>湖北交投武汉都市圈投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>滁州市同创建设投资有限责任公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10639,153 +10649,159 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
-        </is>
-      </c>
-      <c r="AK45" s="3"/>
+          <t>2029-10-27</t>
+        </is>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL45" s="3" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM45" s="3" t="inlineStr">
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY45" s="3" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="AO45" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ45" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR45" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW45" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX45" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY45" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="AZ45" s="3"/>
+      <c r="AZ45" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26西影K1</t>
+          <t>26水发集团MTN005</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>520541.SZ</t>
+          <t>102684257.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2.6</v>
+        <v>7.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2.6</v>
+        <v>7.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
+          <t>1.65 ~ 2.45</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>54.68</v>
+        <v>80.72</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26西影01</t>
+          <t>25水发集团MTN015</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2.36Y+2.00Y</t>
+          <t>2.06Y+N</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.9791</t>
+          <t>2.0496</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>西部电影集团有限公司</t>
+          <t>水发集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C- 22.64</t>
+          <t>C 29.97</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10795,12 +10811,12 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 14:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
@@ -10809,22 +10825,22 @@
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>3.3154</v>
+        <v>1.7714</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
@@ -10834,27 +10850,23 @@
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额为不超过2.60亿元(含2.60亿元),本期债券募集资金扣除发行费用后,拟全部用于偿还西影制片厂和西影数码名下有息债务</t>
+          <t>本期中期票据采取发行金额动态调整机制,基础发行规模人民币0亿元,发行金额上限人民币7亿元,计划用于偿还发行人及子公司的到期有息债务</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>华龙证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3" t="inlineStr">
-        <is>
-          <t>陕西信用增进投资股份有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,长城证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
@@ -10864,153 +10876,155 @@
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>西部电影集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>水发集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM46" s="3" t="inlineStr">
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>次级债权</t>
+        </is>
+      </c>
+      <c r="AY46" s="3" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="AO46" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ46" s="3" t="inlineStr">
-        <is>
-          <t>传媒</t>
-        </is>
-      </c>
-      <c r="AR46" s="3" t="inlineStr">
-        <is>
-          <t>广电</t>
-        </is>
-      </c>
-      <c r="AS46" s="3" t="inlineStr">
-        <is>
-          <t>广电</t>
-        </is>
-      </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>文化传媒</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-27</t>
-        </is>
-      </c>
-      <c r="AV46" s="3" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AW46" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX46" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY46" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="AZ46" s="3"/>
+      <c r="AZ46" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26厦贸Y5</t>
+          <t>26江宁经开MTN007</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>246327.SH</t>
+          <t>102684260.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>1+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>38.96</v>
+        <v>31.68</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>厦贸KY1</t>
+          <t>26江宁经开MTN006</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>359D+N</t>
+          <t>4.97Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.7305</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -11020,12 +11034,12 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>厦门国贸集团股份有限公司</t>
+          <t>南京江宁经济技术开发集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C 28.25</t>
+          <t>C 26.16</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11035,7 +11049,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>10-26 16:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -11049,17 +11063,17 @@
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>2.17</v>
+        <v>7.28</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.77%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -11070,23 +11084,23 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过13亿元（含13亿元），本期债券募集资金扣除发行费用后，拟全部用于向“一带一路”沿线国家（地区）采购业务的营运资金支出，或用于置换3个月内上述相关款项</t>
+          <t>本期中期票据发行金额5.00亿元,拟用于偿还发行人即将到期的债务融资工具本金[23江宁经开PPN003]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,世纪证券有限责任公司,中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,招商证券股份有限公司</t>
+          <t>江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
@@ -11096,12 +11110,12 @@
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>厦门国贸集团股份有限公司2026年面向专业投资者公开发行"一带一路"可续期公司债券(第五期)</t>
+          <t>南京江宁经济技术开发集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -11111,60 +11125,60 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2027-10-27</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM47" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="AO47" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ47" s="3" t="inlineStr">
-        <is>
-          <t>贸易零售</t>
-        </is>
-      </c>
-      <c r="AR47" s="3" t="inlineStr">
-        <is>
-          <t>其他贸易</t>
-        </is>
-      </c>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>其他贸易</t>
-        </is>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>贸易</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV47" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -11172,7 +11186,7 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
@@ -11190,7 +11204,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26滁州同创PPN003</t>
+          <t>26山东同舟MTN001</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -11200,64 +11214,64 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>032680602.IB</t>
+          <t>102684246.IB</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>42.17</v>
+        <v>31.24</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26滁州同创PPN002</t>
+          <t>26同舟02</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>4.93Y+5.00Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.7266</t>
+          <t>2.0351</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>滁州市同创建设投资有限责任公司</t>
+          <t>山东同舟产业控股集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C- 19.99</t>
+          <t>C 25.56</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11267,12 +11281,12 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
@@ -11281,46 +11295,44 @@
         </is>
       </c>
       <c r="U48" s="4" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>1.1</v>
-      </c>
+        <v>1.8636</v>
+      </c>
+      <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>安徽省-滁州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>首期发行金额为5亿元,计划将募集资金用于偿还债务融资工具本金[25滁州同创CP003,25滁州同创CP004]</t>
+          <t>本期中期票据基础发行规模为0亿元,发行金额上限为15亿元,用于偿还本部及子公司流动资金贷款</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
@@ -11335,24 +11347,20 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>滁州市同创建设投资有限责任公司2026年度第三期定向债务融资工具</t>
+          <t>山东同舟产业控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2029-10-27</t>
-        </is>
-      </c>
-      <c r="AK48" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2036-10-27</t>
+        </is>
+      </c>
+      <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -11360,7 +11368,7 @@
       </c>
       <c r="AM48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AN48" s="3" t="inlineStr">
@@ -11370,37 +11378,33 @@
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP48" s="3"/>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AV48" s="3" t="inlineStr">
@@ -11410,7 +11414,7 @@
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">
@@ -11699,8 +11703,12 @@
           <t>1.30 ~ 2.30</t>
         </is>
       </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+      <c r="H50" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>40.4</v>
+      </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -13569,8 +13577,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
+      <c r="H58" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>56.4</v>
+      </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
@@ -16108,7 +16120,7 @@
         <v>4.0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_all_2026-10-26.xlsx
+++ b/data/credit_bond_all_2026-10-26.xlsx
@@ -9364,7 +9364,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26建工3</t>
+          <t>26大唐K1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9374,64 +9374,64 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>246318.SH</t>
+          <t>246333.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>20Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>6.0</v>
+        <v>20.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6.0</v>
+        <v>20.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2.0</v>
+        <v>2.13</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>74.17</v>
+        <v>7.13</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26建工2</t>
+          <t>25大唐集MTN002</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>1.32Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2.0169</t>
+          <t>1.4687</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4500</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>成都建工集团有限公司</t>
+          <t>中国大唐集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.04</t>
+          <t>B- 41.36</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9455,38 +9455,42 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>2.12</v>
+        <v>2.61</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>2.14%~2.24%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z40" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过人民币6亿元(含人民币6亿元)。本期债券募集资金扣除发行费用后,拟将全部用于偿还到期公司债券[21成建工]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9497,7 +9501,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -9507,7 +9511,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>成都建工集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>中国大唐集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9517,7 +9521,7 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
+          <t>2046-10-28</t>
         </is>
       </c>
       <c r="AK40" s="3" t="inlineStr">
@@ -9547,27 +9551,27 @@
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9600,7 +9604,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26大唐K1</t>
+          <t>26泰投01</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9610,19 +9614,19 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>246333.SH</t>
+          <t>284390.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>20Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>20.0</v>
+        <v>17.7</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>20.0</v>
+        <v>17.7</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -9630,44 +9634,44 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>7.13</v>
+        <v>53.68</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>25大唐集MTN002</t>
+          <t>26泰兴城投PPN004</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>1.32Y</t>
+          <t>2.77Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.4687</t>
+          <t>1.6655</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/1.4500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>中国大唐集团有限公司</t>
+          <t>泰兴市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 41.36</t>
+          <t>C- 11.34</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9677,7 +9681,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>10-26 16:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9691,42 +9695,38 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>2.61</v>
+        <v>2.4791</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>2.14%~2.24%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
+          <t>本期公司债券募集资金扣除发行费用后,仅用于偿还“23泰投01”和“24泰投01”到期的公司债券本金。[23泰投01,24泰投01]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>东吴证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
@@ -9747,24 +9747,20 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>中国大唐集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>泰兴市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2046-10-28</t>
-        </is>
-      </c>
-      <c r="AK41" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-28</t>
+        </is>
+      </c>
+      <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
           <t>2026-11-02</t>
@@ -9772,7 +9768,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN41" s="3" t="inlineStr">
@@ -9782,32 +9778,32 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9840,59 +9836,59 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26泰投01</t>
+          <t>26桂交投MTN010</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>284390.SH</t>
+          <t>102684264.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>17.7</v>
+        <v>10.0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>17.7</v>
+        <v>10.0</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.04</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>53.68</v>
+        <v>53.39</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26泰兴城投PPN004</t>
+          <t>24桂交投MTN010B</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.77Y</t>
+          <t>7.59Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.6655</t>
+          <t>2.1312</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -9902,12 +9898,12 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>泰兴市城市投资发展集团有限公司</t>
+          <t>广西交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 11.34</t>
+          <t>C 27.26</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9917,58 +9913,60 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>2.4791</v>
-      </c>
-      <c r="V42" s="3"/>
+        <v>2.38</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>3.4</v>
+      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,仅用于偿还“23泰投01”和“24泰投01”到期的公司债券本金。[23泰投01,24泰投01]</t>
+          <t>本期中期票据发行金额10亿元,计划全部用于归还发行人存量债务融资工具[25桂交投CP006,25桂交投CP007]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9978,153 +9976,155 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>泰兴市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>广西交通投资集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
+          <t>2033-10-27</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY42" s="3" t="inlineStr">
+        <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AO42" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ42" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR42" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV42" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW42" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX42" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY42" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="AZ42" s="3"/>
+      <c r="AZ42" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26桂交投MTN010</t>
+          <t>26交子02</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>102684264.IB</t>
+          <t>284366.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.04</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>53.39</v>
+        <v>24.68</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>24桂交投MTN010B</t>
+          <t>26交子01</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>7.59Y</t>
+          <t>2.46Y+2.00Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2.1312</t>
+          <t>1.6708</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -10134,12 +10134,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>广西交通投资集团有限公司</t>
+          <t>成都交子公园金融商务区投资开发有限责任公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C 27.26</t>
+          <t>C- 24.22</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10149,60 +10149,58 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>3.4</v>
-      </c>
+        <v>5.78</v>
+      </c>
+      <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额10亿元,计划全部用于归还发行人存量债务融资工具[25桂交投CP006,25桂交投CP007]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还到期的有息债务[21交子公园MTN001]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -10212,73 +10210,73 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>广西交通投资集团有限公司2026年度第十期中期票据</t>
+          <t>成都交子公园金融商务区投资开发有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2033-10-27</t>
+          <t>2031-10-28</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="AM43" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6*无效</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-28</t>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
@@ -10288,7 +10286,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -10301,81 +10299,79 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ43" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ43" s="3"/>
     </row>
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26交子02</t>
+          <t>26安阳钢铁CP001</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-27 18:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>284366.SH</t>
+          <t>042680355.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>24.68</v>
+        <v>212.01</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26交子01</t>
+          <t>26安阳钢铁MTN006(科创债)</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2.46Y+2.00Y</t>
+          <t>337D+3.00Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.6708</t>
+          <t>2.5000</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.5000</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>成都交子公园金融商务区投资开发有限责任公司</t>
+          <t>安阳钢铁集团有限责任公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 24.22</t>
+          <t>C- 15.97</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10385,7 +10381,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10399,17 +10395,17 @@
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>5.78</v>
+        <v>0.8</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>2.65%~2.69%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10420,23 +10416,23 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>河南省-安阳市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还到期的有息债务[21交子公园MTN001]</t>
+          <t>发行人本期债务融资工具基础发行规模0亿元,发行金额上限为人民币5亿元,拟全部用于偿还发行人及合并范围子公司有息负债。[25安阳钢铁MTN006(科创债)]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -10446,75 +10442,75 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>成都交子公园金融商务区投资开发有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>安阳钢铁集团有限责任公司2026年度第一期短期融资券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
+          <t>2027-10-28</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>普钢</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM44" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AO44" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>6*无效</t>
-        </is>
-      </c>
-      <c r="AQ44" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR44" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT44" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU44" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-28</t>
-        </is>
-      </c>
       <c r="AV44" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -10522,7 +10518,7 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10532,15 +10528,17 @@
       </c>
       <c r="AY44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="AZ44" s="3"/>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AZ44" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26安阳钢铁CP001</t>
+          <t>26佛山建设MTN003</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10550,64 +10548,64 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>042680355.IB</t>
+          <t>102684247.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>3.3</v>
+        <v>1.66</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>212.01</v>
+        <v>40.4</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26安阳钢铁MTN006(科创债)</t>
+          <t>24佛山建设MTN003</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>337D+3.00Y</t>
+          <t>2.92Y+N</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2.5000</t>
+          <t>1.6628</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/2.5000</t>
+          <t>--/1.6400</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>安阳钢铁集团有限责任公司</t>
+          <t>佛山市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 15.97</t>
+          <t>C+ 30.88</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10622,7 +10620,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -10631,44 +10629,48 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>0.8</v>
+        <v>4.04</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2.65%~2.69%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z45" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>河南省-安阳市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具基础发行规模0亿元,发行金额上限为人民币5亿元,拟全部用于偿还发行人及合并范围子公司有息负债。[25安阳钢铁MTN006(科创债)]</t>
+          <t>本次拟发行15亿元长期限含权中期票据，主要用途为偿还到期债务融资工具【24 佛山建设MTN001 】</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>招商银行股份有限公司,长江证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10683,7 +10685,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>安阳钢铁集团有限责任公司2026年度第一期短期融资券</t>
+          <t>佛山市建设发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10693,10 +10695,14 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2027-10-28</t>
-        </is>
-      </c>
-      <c r="AK45" s="3"/>
+          <t>2029-10-28</t>
+        </is>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL45" s="3" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -10704,7 +10710,7 @@
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10714,32 +10720,32 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10754,12 +10760,12 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY45" s="3" t="inlineStr">
@@ -10768,80 +10774,80 @@
         </is>
       </c>
       <c r="AZ45" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26佛山建设MTN003</t>
+          <t>26璞信K2</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>10-27 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>102684247.IB</t>
+          <t>520543.SZ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>40.4</v>
+        <v>47.68</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>24佛山建设MTN003</t>
+          <t>26璞信K1</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2.92Y+N</t>
+          <t>2.67Y+2.00Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.6628</t>
+          <t>1.9008</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/1.6400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>佛山市建设发展集团有限公司</t>
+          <t>四川璞信产融投资有限责任公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.88</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10851,62 +10857,58 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>4.04</v>
+        <v>2.73</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>四川省-泸州市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本次拟发行15亿元长期限含权中期票据，主要用途为偿还到期债务融资工具【24 佛山建设MTN001 】</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于置换发行前12个月内的科技创新领域相关投资支出</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,长江证券股份有限公司</t>
+          <t>国信证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
@@ -10916,77 +10918,69 @@
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>佛山市建设发展集团有限公司2026年度第三期中期票据</t>
+          <t>四川璞信产融投资有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
-        </is>
-      </c>
-      <c r="AK46" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-27</t>
+        </is>
+      </c>
+      <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AN46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP46" s="3"/>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR46" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS46" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU46" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-27</t>
         </is>
       </c>
       <c r="AV46" s="3" t="inlineStr">
@@ -10996,27 +10990,25 @@
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="AZ46" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="AZ46" s="3"/>
     </row>
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26璞信K2</t>
+          <t>26西影K1</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -11026,7 +11018,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>520543.SZ</t>
+          <t>520541.SZ</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -11035,55 +11027,55 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>4.0</v>
+        <v>2.6</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4.0</v>
+        <v>2.6</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.70 ~ 2.50</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>47.68</v>
+        <v>54.68</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26璞信K1</t>
+          <t>26西影01</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.67Y+2.00Y</t>
+          <t>2.36Y+2.00Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.9008</t>
+          <t>1.9791</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>四川璞信产融投资有限责任公司</t>
+          <t>西部电影集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>D+ 7.92</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11107,41 +11099,49 @@
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>2.73</v>
+        <v>3.3154</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z47" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>四川省-泸州市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于置换发行前12个月内的科技创新领域相关投资支出</t>
+          <t>本期债券发行总额为不超过2.60亿元(含2.60亿元),本期债券募集资金扣除发行费用后,拟全部用于偿还西影制片厂和西影数码名下有息债务</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD47" s="3"/>
+          <t>华龙证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr">
+        <is>
+          <t>陕西信用增进投资股份有限公司</t>
+        </is>
+      </c>
       <c r="AE47" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>四川璞信产融投资有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
+          <t>西部电影集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="AM47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN47" s="3" t="inlineStr">
@@ -11190,28 +11190,32 @@
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP47" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>传媒</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -11221,7 +11225,7 @@
       </c>
       <c r="AV47" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW47" s="3" t="inlineStr">
@@ -11244,7 +11248,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26西影K1</t>
+          <t>26遂昌01</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -11254,64 +11258,64 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>520541.SZ</t>
+          <t>284370.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2.6</v>
+        <v>10.0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2.6</v>
+        <v>10.0</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>54.68</v>
+        <v>60.68</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26西影01</t>
+          <t>26高安01</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.36Y+2.00Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.9791</t>
+          <t>2.0118</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>2.1100/2.0000</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>西部电影集团有限公司</t>
+          <t>遂昌县国有资本投资运营集团有限责任公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.92</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11331,11 +11335,11 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="U48" s="4" t="n">
-        <v>3.3154</v>
+        <v>2.48</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
@@ -11345,39 +11349,31 @@
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>浙江省-丽水市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额为不超过2.60亿元(含2.60亿元),本期债券募集资金扣除发行费用后,拟全部用于偿还西影制片厂和西影数码名下有息债务</t>
+          <t>本期债券的募集资金扣除发行费用后,全部用于偿还到期的公司债券本金。[23遂昌01]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>华龙证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD48" s="3" t="inlineStr">
-        <is>
-          <t>陕西信用增进投资股份有限公司</t>
-        </is>
-      </c>
+          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -11390,12 +11386,12 @@
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>西部电影集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>遂昌县国有资本投资运营集团有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11405,13 +11401,13 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2031-10-29</t>
         </is>
       </c>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM48" s="3" t="inlineStr">
@@ -11421,52 +11417,52 @@
       </c>
       <c r="AN48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7*无效</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>传媒</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>广电</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>广电</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
         <is>
-          <t>2029-10-27</t>
+          <t/>
         </is>
       </c>
       <c r="AV48" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">
@@ -11484,17 +11480,17 @@
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26遂昌01</t>
+          <t>26柯经02</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>284370.SH</t>
+          <t>284315.SH</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -11503,55 +11499,55 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>60.68</v>
+        <v>47.68</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26高安01</t>
+          <t>26柯经01</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>4.42Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>2.0118</t>
+          <t>1.8456</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>2.1100/2.0000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>遂昌县国有资本投资运营集团有限责任公司</t>
+          <t>绍兴柯桥经济技术开发区控股集团有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B+ 57.88</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11571,21 +11567,21 @@
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="U49" s="4" t="n">
-        <v>2.48</v>
+        <v>3.0</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
@@ -11596,17 +11592,17 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>浙江省-丽水市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后,全部用于偿还到期的公司债券本金。[23遂昌01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还公司债券本金。[23柯控01]</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
+          <t>浙商证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
@@ -11627,7 +11623,7 @@
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>遂昌县国有资本投资运营集团有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>绍兴柯桥经济技术开发区控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11637,13 +11633,13 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2031-10-29</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="AM49" s="3" t="inlineStr">
@@ -11653,7 +11649,7 @@
       </c>
       <c r="AN49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AO49" s="3" t="inlineStr">
@@ -11663,27 +11659,27 @@
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>7*无效</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
@@ -11716,22 +11712,22 @@
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26尚太科技SCP001</t>
+          <t>26建工3</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>012682539.IB</t>
+          <t>246318.SH</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -11742,33 +11738,33 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1.8</v>
+        <v>2.0</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>62.5</v>
+        <v>74.17</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>26璞泰来SCP001</t>
+          <t>26建工2</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>155D</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.5567</t>
+          <t>2.0169</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -11778,12 +11774,12 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>石家庄尚太科技股份有限公司</t>
+          <t>成都建工集团有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>D+ 9.04</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11793,33 +11789,31 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 16:00</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>1.6333</v>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>2.44</v>
-      </c>
+        <v>2.12</v>
+      </c>
+      <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.80%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
@@ -11830,38 +11824,38 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>河北省-石家庄市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期超短期融资券募集资金5亿元用于补充本部及子公司的流动资金,1亿元用于偿还银行借款。</t>
+          <t>本期债券发行金额为不超过人民币6亿元(含人民币6亿元)。本期债券募集资金扣除发行费用后,拟将全部用于偿还到期公司债券[21成建工]</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,交通银行股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF50" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG50" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>石家庄尚太科技股份有限公司2026年度第一期超短期融资券</t>
+          <t>成都建工集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
@@ -11871,7 +11865,7 @@
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2027-04-25</t>
+          <t>2029-10-28</t>
         </is>
       </c>
       <c r="AK50" s="3" t="inlineStr">
@@ -11881,19 +11875,19 @@
       </c>
       <c r="AL50" s="3" t="inlineStr">
         <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="AM50" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -11901,27 +11895,27 @@
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>其他轻工制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11949,14 +11943,12 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ50" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ50" s="3"/>
     </row>
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26广晟MTN004</t>
+          <t>26尚太科技SCP001</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -11966,64 +11958,64 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>102684255.IB</t>
+          <t>012682539.IB</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>23.68</v>
+        <v>62.5</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>26广晟MTN003</t>
+          <t>26璞泰来SCP001</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>4.80Y</t>
+          <t>155D</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.6871</t>
+          <t>1.5567</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>广东省广晟控股集团有限公司</t>
+          <t>石家庄尚太科技股份有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C 28.24</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -12038,7 +12030,7 @@
       </c>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T51" s="3" t="inlineStr">
@@ -12047,49 +12039,51 @@
         </is>
       </c>
       <c r="U51" s="4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V51" s="3"/>
+        <v>1.6333</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>2.44</v>
+      </c>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.76%~1.80%</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>河北省-石家庄市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额不超过10亿元,拟用于偿还有息债务</t>
+          <t>发行人拟将本期超短期融资券募集资金5亿元用于补充本部及子公司的流动资金,1亿元用于偿还银行借款。</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中信银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG51" s="3" t="inlineStr">
@@ -12099,7 +12093,7 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>广东省广晟控股集团有限公司2026年度第四期中期票据</t>
+          <t>石家庄尚太科技股份有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -12109,10 +12103,14 @@
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
-        </is>
-      </c>
-      <c r="AK51" s="3"/>
+          <t>2027-04-25</t>
+        </is>
+      </c>
+      <c r="AK51" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL51" s="3" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -12120,7 +12118,7 @@
       </c>
       <c r="AM51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AN51" s="3" t="inlineStr">
@@ -12135,27 +12133,27 @@
       </c>
       <c r="AP51" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>其他轻工制造</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -12183,12 +12181,14 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ51" s="3"/>
+      <c r="AZ51" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26青岛海控MTN004</t>
+          <t>26广晟MTN004</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -12198,19 +12198,19 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>102684252.IB</t>
+          <t>102684255.IB</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -12218,44 +12218,44 @@
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>42.17</v>
+        <v>23.68</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>26青岛海控MTN003</t>
+          <t>26广晟MTN003</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>4.80Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.7137</t>
+          <t>1.6871</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>1.7450/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>青岛西海岸新区海洋控股集团有限公司</t>
+          <t>广东省广晟控股集团有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C 28.22</t>
+          <t>C 28.24</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="S52" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="T52" s="3" t="inlineStr">
@@ -12279,19 +12279,17 @@
         </is>
       </c>
       <c r="U52" s="4" t="n">
-        <v>4.2857</v>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>2.06</v>
-      </c>
+        <v>3.7</v>
+      </c>
+      <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.62%~1.72%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
@@ -12302,17 +12300,17 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模不超过7亿元,全部用于偿还发行人有息债务本金[26青岛海控SCP001]</t>
+          <t>本期债务融资工具发行金额不超过10亿元,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
@@ -12333,7 +12331,7 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>青岛西海岸新区海洋控股集团有限公司2026年度第四期中期票据</t>
+          <t>广东省广晟控股集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -12343,14 +12341,10 @@
       </c>
       <c r="AJ52" s="3" t="inlineStr">
         <is>
-          <t>2029-10-27</t>
-        </is>
-      </c>
-      <c r="AK52" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-27</t>
+        </is>
+      </c>
+      <c r="AK52" s="3"/>
       <c r="AL52" s="3" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -12368,12 +12362,12 @@
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
@@ -12383,17 +12377,17 @@
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12421,75 +12415,79 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ52" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ52" s="3"/>
     </row>
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26江金Y2(取消发行)</t>
+          <t>26青岛海控MTN004</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>DY246255.SH</t>
+          <t>102684252.IB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F53" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>42.17</v>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26江金02</t>
+          <t>26青岛海控MTN003</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2.42Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.6767</t>
+          <t>1.7137</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7450/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>江西省金控投资集团有限公司</t>
+          <t>青岛西海岸新区海洋控股集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 13.00</t>
+          <t>C 28.22</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12499,29 +12497,33 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>10-26 16:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>4.2857</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>2.06</v>
+      </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
@@ -12532,23 +12534,23 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟用于偿还到期有息债务</t>
+          <t>本期中期票据发行规模不超过7亿元,全部用于偿还发行人有息债务本金[26青岛海控SCP001]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
+          <t>南京银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
@@ -12558,12 +12560,12 @@
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>江西省金控投资集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)(品种二)(取消发行)</t>
+          <t>青岛西海岸新区海洋控股集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12573,153 +12575,153 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
-        </is>
-      </c>
-      <c r="AK53" s="3"/>
+          <t>2029-10-27</t>
+        </is>
+      </c>
+      <c r="AK53" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL53" s="3" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM53" s="3" t="inlineStr">
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY53" s="3" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AO53" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ53" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR53" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS53" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT53" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU53" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV53" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW53" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX53" s="3" t="inlineStr">
-        <is>
-          <t>次级债权</t>
-        </is>
-      </c>
-      <c r="AY53" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="AZ53" s="3"/>
+      <c r="AZ53" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26苏元禾MTN003A(科创债)</t>
+          <t>26江金Y2(取消发行)</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>102684248.IB</t>
+          <t>DY246255.SH</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>22.17</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>26苏元禾MTN002A(科创债)</t>
+          <t>26江金02</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2.85Y</t>
+          <t>2.42Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.5990</t>
+          <t>1.6767</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>1.6000/1.5894</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>苏州元禾控股股份有限公司</t>
+          <t>江西省金控投资集团有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C 28.76</t>
+          <t>C- 13.00</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12729,33 +12731,29 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>10-26 09:00</t>
+          <t>10-26 16:00</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>1.47</v>
-      </c>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.64%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
@@ -12766,23 +12764,23 @@
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行拟募集资金10亿元,全部用于置换发行人一年以内用于科技创新领域基金出资的自有资金投入。</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟用于偿还到期有息债务</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
       <c r="AE54" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF54" s="3" t="inlineStr">
@@ -12792,12 +12790,12 @@
       </c>
       <c r="AG54" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>苏州元禾控股股份有限公司2026年度第三期科技创新债券(品种一)</t>
+          <t>江西省金控投资集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12807,35 +12805,35 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2029-10-27</t>
-        </is>
-      </c>
-      <c r="AK54" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-28</t>
+        </is>
+      </c>
+      <c r="AK54" s="3"/>
       <c r="AL54" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="AM54" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>金融</t>
         </is>
       </c>
-      <c r="AP54" s="3"/>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -12843,12 +12841,12 @@
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
@@ -12868,12 +12866,12 @@
       </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX54" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY54" s="3" t="inlineStr">
@@ -12886,17 +12884,17 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26亳交01(取消发行)</t>
+          <t>26苏元禾MTN003A(科创债)</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>DY284270.SH</t>
+          <t>102684248.IB</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -12905,49 +12903,55 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F55" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
+          <t>1.40 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>22.17</v>
+      </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>25亳交03</t>
+          <t>26苏元禾MTN002A(科创债)</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2.01Y</t>
+          <t>2.85Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.7087</t>
+          <t>1.5990</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>1.6000/1.5894</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>亳州交通投资控股集团有限公司</t>
+          <t>苏州元禾控股股份有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C- 22.69</t>
+          <t>C 28.76</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12957,60 +12961,60 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>10-26 16:00</t>
+          <t>10-26 09:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>1.47</v>
+      </c>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.54%~1.64%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>安徽省-亳州市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为不超过5亿元(含)。本期公司债券募集资金扣除发行费用后,拟用于偿还公司到期的公司债券本金。如本期债券募集资金到账前,发行人已使用自有资金偿还上述公司债券本金,则本期公司债券募集资金将全部用于置换发行人用于偿还上述公司债券本金的自有资金。[23亳交02]</t>
+          <t>本期债务融资工具发行拟募集资金10亿元,全部用于置换发行人一年以内用于科技创新领域基金出资的自有资金投入。</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD55" s="3" t="inlineStr">
-        <is>
-          <t>建安投资控股集团有限公司</t>
-        </is>
-      </c>
+          <t>上海浦东发展银行股份有限公司,中国光大银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD55" s="3"/>
       <c r="AE55" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF55" s="3" t="inlineStr">
@@ -13020,82 +13024,78 @@
       </c>
       <c r="AG55" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>亳州交通投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)(取消发行)</t>
+          <t>苏州元禾控股股份有限公司2026年度第三期科技创新债券(品种一)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
+          <t>2029-10-27</t>
         </is>
       </c>
       <c r="AK55" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL55" s="3" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM55" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AO55" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AQ55" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR55" s="3" t="inlineStr">
-        <is>
-          <t>综合交运基础设施</t>
-        </is>
-      </c>
-      <c r="AS55" s="3" t="inlineStr">
-        <is>
-          <t>综合交运基础设施</t>
-        </is>
-      </c>
-      <c r="AT55" s="3" t="inlineStr">
-        <is>
-          <t>公交</t>
-        </is>
-      </c>
-      <c r="AU55" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV55" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW55" s="3" t="inlineStr">
@@ -13118,7 +13118,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26华证C1</t>
+          <t>26亳交01(取消发行)</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>246290.SH</t>
+          <t>DY284270.SH</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -13137,55 +13137,49 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>34.17</v>
-      </c>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26华宝证券CP004</t>
+          <t>25亳交03</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>228D</t>
+          <t>2.01Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.4810</t>
+          <t>1.7087</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>华宝证券股份有限公司</t>
+          <t>亳州交通投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C- 13.13</t>
+          <t>C- 22.69</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13195,7 +13189,7 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 16:00</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -13208,50 +13202,52 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="U56" s="4" t="n">
-        <v>4.26</v>
-      </c>
+      <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>安徽省-亳州市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后,拟将不超过15.00亿元(含)的金额全部用于偿还有息债务。</t>
+          <t>本期发行金额为不超过5亿元(含)。本期公司债券募集资金扣除发行费用后,拟用于偿还公司到期的公司债券本金。如本期债券募集资金到账前,发行人已使用自有资金偿还上述公司债券本金,则本期公司债券募集资金将全部用于置换发行人用于偿还上述公司债券本金的自有资金。[23亳交02]</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD56" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr">
+        <is>
+          <t>建安投资控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE56" s="3" t="inlineStr">
         <is>
-          <t>证券公司次级债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF56" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG56" s="3" t="inlineStr">
@@ -13261,12 +13257,12 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>华宝证券股份有限公司2026年面向专业投资者公开发行次级公司债券(第一期)(品种一)</t>
+          <t>亳州交通投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ56" s="3" t="inlineStr">
@@ -13286,7 +13282,7 @@
       </c>
       <c r="AM56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN56" s="3" t="inlineStr">
@@ -13296,32 +13292,32 @@
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合交运基础设施</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>综合交运基础设施</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -13331,7 +13327,7 @@
       </c>
       <c r="AV56" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW56" s="3" t="inlineStr">
@@ -13341,7 +13337,7 @@
       </c>
       <c r="AX56" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY56" s="3" t="inlineStr">
@@ -13354,7 +13350,7 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26润租GC4</t>
+          <t>26华证C1</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -13364,64 +13360,64 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>525070.SZ</t>
+          <t>246290.SH</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F57" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>25.68</v>
+        <v>34.17</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26润租G2</t>
+          <t>26华宝证券CP004</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>2.91Y+2.00Y</t>
+          <t>228D</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.6044</t>
+          <t>1.4810</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>--/1.5800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>华润融资租赁有限公司</t>
+          <t>华宝证券股份有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C 26.93</t>
+          <t>C- 13.13</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13431,7 +13427,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>10-26 14:00</t>
+          <t>10-26 15:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -13441,52 +13437,48 @@
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U57" s="4" t="n">
-        <v>3.08</v>
+        <v>4.26</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z57" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟发行金额为不超过5.00亿元,募集资金扣除发行费用后,拟将不超过38,462.80万元用于置换本期债券发行前12个月内发行人用于绿色融资租赁项目投放的自有资金,不超过11,537.20万元用于偿还发行人绿色融资租赁项目投放使用的有息债务。</t>
+          <t>本期债券的募集资金扣除发行费用后,拟将不超过15.00亿元(含)的金额全部用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司次级债</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
@@ -13496,12 +13488,12 @@
       </c>
       <c r="AG57" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>华润融资租赁有限公司2026年面向专业投资者公开发行碳中和绿色公司债券(第四期)</t>
+          <t>华宝证券股份有限公司2026年面向专业投资者公开发行次级公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13511,10 +13503,14 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
-        </is>
-      </c>
-      <c r="AK57" s="3"/>
+          <t>2029-10-28</t>
+        </is>
+      </c>
+      <c r="AK57" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL57" s="3" t="inlineStr">
         <is>
           <t/>
@@ -13522,12 +13518,12 @@
       </c>
       <c r="AM57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AN57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AO57" s="3" t="inlineStr">
@@ -13537,7 +13533,7 @@
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
@@ -13547,22 +13543,22 @@
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
         <is>
-          <t>2029-10-27</t>
+          <t/>
         </is>
       </c>
       <c r="AV57" s="3" t="inlineStr">
@@ -13572,12 +13568,12 @@
       </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX57" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY57" s="3" t="inlineStr">
@@ -13590,7 +13586,7 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26华证C2</t>
+          <t>26润租GC4</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13600,64 +13596,64 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>246291.SH</t>
+          <t>525070.SZ</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>44.68</v>
+        <v>25.68</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26华宝证券CP004</t>
+          <t>26润租G2</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>228D</t>
+          <t>2.91Y+2.00Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.4810</t>
+          <t>1.6044</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5800</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>华宝证券股份有限公司</t>
+          <t>华润融资租赁有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>C- 13.13</t>
+          <t>C 26.93</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13667,7 +13663,7 @@
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 14:00</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
@@ -13677,48 +13673,52 @@
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z58" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后,拟将不超过15.00亿元(含)的金额全部用于偿还有息债务。</t>
+          <t>本期债券拟发行金额为不超过5.00亿元,募集资金扣除发行费用后,拟将不超过38,462.80万元用于置换本期债券发行前12个月内发行人用于绿色融资租赁项目投放的自有资金,不超过11,537.20万元用于偿还发行人绿色融资租赁项目投放使用的有息债务。</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>广发证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>证券公司次级债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
@@ -13728,12 +13728,12 @@
       </c>
       <c r="AG58" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>华宝证券股份有限公司2026年面向专业投资者公开发行次级公司债券(第一期)(品种二)</t>
+          <t>华润融资租赁有限公司2026年面向专业投资者公开发行碳中和绿色公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2031-10-28</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -13754,12 +13754,12 @@
       </c>
       <c r="AM58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AN58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AO58" s="3" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
@@ -13779,22 +13779,22 @@
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-27</t>
         </is>
       </c>
       <c r="AV58" s="3" t="inlineStr">
@@ -13804,12 +13804,12 @@
       </c>
       <c r="AW58" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX58" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY58" s="3" t="inlineStr">
@@ -13822,7 +13822,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26青城13(取消发行)</t>
+          <t>26华证C2</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13832,122 +13832,130 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>DY246325.SH</t>
+          <t>246291.SH</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>5+3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F59" s="3"/>
+        <v>7.5</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>44.68</v>
+      </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>26华宝证券CP004</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>228D</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>1.4810</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>华宝证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>C- 13.13</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>10-26 15:00</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>26青岛城投MTN006</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>4.80Y+10.00Y</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>1.7342</t>
-        </is>
-      </c>
-      <c r="N59" s="3" t="inlineStr">
-        <is>
-          <t>--/1.7000</t>
-        </is>
-      </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>青岛城市建设投资(集团)有限责任公司</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="inlineStr">
-        <is>
-          <t>B- 41.38</t>
-        </is>
-      </c>
-      <c r="Q59" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
-        <is>
-          <t>10-26 16:00</t>
-        </is>
-      </c>
-      <c r="S59" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="U59" s="3"/>
+      <c r="U59" s="4" t="n">
+        <v>2.47</v>
+      </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过21.20亿元(含21.20亿元)募集资金拟全部用于偿还发行人到期的公司债券本金[23青城10,23青城11]</t>
+          <t>本期债券的募集资金扣除发行费用后,拟将不超过15.00亿元(含)的金额全部用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司,长江证券股份有限公司,中邮证券有限责任公司,中泰证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司次级债</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG59" s="3" t="inlineStr">
@@ -13957,7 +13965,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>青岛城市建设投资(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)(取消发行)</t>
+          <t>华宝证券股份有限公司2026年面向专业投资者公开发行次级公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13967,7 +13975,7 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2036-10-28</t>
+          <t>2031-10-28</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
@@ -13988,32 +13996,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -14028,12 +14036,12 @@
       </c>
       <c r="AW59" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX59" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY59" s="3" t="inlineStr">
@@ -14046,7 +14054,7 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26皖通03</t>
+          <t>26青城13(取消发行)</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -14056,64 +14064,58 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>246308.SH</t>
+          <t>DY246325.SH</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+3+2</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>7.0</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>17.17</v>
-      </c>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26皖通01</t>
+          <t>26青岛城投MTN006</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2.76Y</t>
+          <t>4.80Y+10.00Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.5396</t>
+          <t>1.7342</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>安徽皖通高速公路股份有限公司</t>
+          <t>青岛城市建设投资(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.90</t>
+          <t>B- 41.38</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14136,18 +14138,16 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="U60" s="4" t="n">
-        <v>3.47</v>
-      </c>
+      <c r="U60" s="3"/>
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.62%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -14158,17 +14158,17 @@
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过7.00亿元(含7.00亿元),本期公司债券募集资金扣除发行费用后,拟将不超过3.00亿元(含3.00亿元)用于固定资产项目投资,拟将不超过3.00亿元(含3.00亿元)用于补充流动资金,拟将不超过1.00亿元(含1.00亿元)用于偿还有息债务。</t>
+          <t>本期债券发行规模不超过21.20亿元(含21.20亿元)募集资金拟全部用于偿还发行人到期的公司债券本金[23青城10,23青城11]</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司,长江证券股份有限公司,中邮证券有限责任公司,中泰证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>安徽皖通高速公路股份有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
+          <t>青岛城市建设投资(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -14199,17 +14199,13 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
-        </is>
-      </c>
-      <c r="AK60" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2036-10-28</t>
+        </is>
+      </c>
+      <c r="AK60" s="3"/>
       <c r="AL60" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t/>
         </is>
       </c>
       <c r="AM60" s="3" t="inlineStr">
@@ -14229,27 +14225,27 @@
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -14264,7 +14260,7 @@
       </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX60" s="3" t="inlineStr">
@@ -14282,74 +14278,74 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26青山湖PPN001</t>
+          <t>26皖通03</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>032680601.IB</t>
+          <t>246308.SH</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>6.9</v>
+        <v>3.5</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>6.9</v>
+        <v>7.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>36.68</v>
+        <v>17.17</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>26科投01</t>
+          <t>26皖通01</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>4.20Y</t>
+          <t>2.76Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.7685</t>
+          <t>1.5396</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>浙江杭州青山湖科技城投资集团有限公司</t>
+          <t>安徽皖通高速公路股份有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>B- 43.12</t>
+          <t>D+ 7.90</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14359,58 +14355,58 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>10-26 14:00</t>
+          <t>10-26 16:00</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U61" s="4" t="n">
-        <v>4.8522</v>
+        <v>3.47</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.52%~1.62%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具发行基础规模0亿元、发行金额上限6.90亿元,拟全部用于偿还发行人到期的债务融资工具本金[21青山湖科MTN001]</t>
+          <t>本期债券发行规模不超过7.00亿元(含7.00亿元),本期公司债券募集资金扣除发行费用后,拟将不超过3.00亿元(含3.00亿元)用于固定资产项目投资,拟将不超过3.00亿元(含3.00亿元)用于补充流动资金,拟将不超过1.00亿元(含1.00亿元)用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,江苏银行股份有限公司,杭州银行股份有限公司,中国邮政储蓄银行股份有限公司,中信银行股份有限公司,宁波银行股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF61" s="3" t="inlineStr">
@@ -14420,56 +14416,72 @@
       </c>
       <c r="AG61" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>浙江杭州青山湖科技城投资集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>安徽皖通高速公路股份有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
-        </is>
-      </c>
-      <c r="AK61" s="3"/>
+          <t>2029-10-28</t>
+        </is>
+      </c>
+      <c r="AK61" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL61" s="3" t="inlineStr">
         <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="AM61" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ61" s="3"/>
-      <c r="AR61" s="3"/>
-      <c r="AS61" s="3"/>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -14497,24 +14509,22 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ61" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ61" s="3"/>
     </row>
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26余工01</t>
+          <t>26青山湖PPN001</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>10-26 19:00</t>
+          <t>10-26 18:00</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>284353.SH</t>
+          <t>032680601.IB</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -14523,21 +14533,21 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>5.0</v>
+        <v>6.9</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>5.0</v>
+        <v>6.9</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>46.68</v>
+        <v>36.68</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -14546,32 +14556,32 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>25余姚工业PPN001</t>
+          <t>26科投01</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>3.42Y</t>
+          <t>4.20Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.7140</t>
+          <t>1.7685</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>浙江余姚工业园区开发建设投资有限公司</t>
+          <t>浙江杭州青山湖科技城投资集团有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C- 17.40</t>
+          <t>B- 43.12</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14581,12 +14591,12 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>10-26 15:00</t>
+          <t>10-26 14:00</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
@@ -14595,44 +14605,44 @@
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>3.84</v>
+        <v>4.8522</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将50,000.00万元全部用于偿还到期的公司债券本金[21余工02,21余工03]</t>
+          <t>发行人本次定向债务融资工具发行基础规模0亿元、发行金额上限6.90亿元,拟全部用于偿还发行人到期的债务融资工具本金[21青山湖科MTN001]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>甬兴证券有限公司,东海证券股份有限公司,浙商证券股份有限公司,平安证券股份有限公司</t>
+          <t>国信证券股份有限公司,江苏银行股份有限公司,杭州银行股份有限公司,中国邮政储蓄银行股份有限公司,中信银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
@@ -14642,12 +14652,12 @@
       </c>
       <c r="AG62" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>浙江余姚工业园区开发建设投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>浙江杭州青山湖科技城投资集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14663,7 +14673,7 @@
       <c r="AK62" s="3"/>
       <c r="AL62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AM62" s="3" t="inlineStr">
@@ -14683,27 +14693,15 @@
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ62" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR62" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS62" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ62" s="3"/>
+      <c r="AR62" s="3"/>
+      <c r="AS62" s="3"/>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14731,12 +14729,14 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AZ62" s="3"/>
+      <c r="AZ62" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26堰鑫01</t>
+          <t>26余工01</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>520552.SZ</t>
+          <t>284353.SH</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -14755,109 +14755,113 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>8.25</v>
+        <v>5.0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>8.25</v>
+        <v>5.0</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>61.68</v>
+        <v>46.68</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>25余姚工业PPN001</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>3.42Y</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>1.7140</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>浙江余姚工业园区开发建设投资有限公司</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>C- 17.40</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>10-26 15:00</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N63" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>十堰城鑫产业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q63" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="R63" s="3" t="inlineStr">
-        <is>
-          <t>10-26 15:00</t>
-        </is>
-      </c>
-      <c r="S63" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>4.45</v>
+        <v>3.84</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>湖北省-十堰市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟将8.25亿元偿还有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将50,000.00万元全部用于偿还到期的公司债券本金[21余工02,21余工03]</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD63" s="3" t="inlineStr">
-        <is>
-          <t>江西省信用融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>甬兴证券有限公司,东海证券股份有限公司,浙商证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD63" s="3"/>
       <c r="AE63" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -14870,12 +14874,12 @@
       </c>
       <c r="AG63" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>十堰城鑫产业投资集团有限公司2026年面向专业投资者非公开公司债券(第一期)</t>
+          <t>浙江余姚工业园区开发建设投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14891,53 +14895,57 @@
       <c r="AK63" s="3"/>
       <c r="AL63" s="3" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ63" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM63" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="AO63" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP63" s="3"/>
-      <c r="AQ63" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR63" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS63" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT63" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU63" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV63" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW63" s="3" t="inlineStr">
@@ -14960,17 +14968,17 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26柯经02</t>
+          <t>26堰鑫01</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>10-26 18:00</t>
+          <t>10-26 19:00</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>284315.SH</t>
+          <t>520552.SZ</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -14979,10 +14987,10 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2.0</v>
+        <v>8.25</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2.0</v>
+        <v>8.25</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
@@ -14990,29 +14998,21 @@
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>47.68</v>
+        <v>61.68</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>26柯经01</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>4.42Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.8456</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -15022,12 +15022,12 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>绍兴柯桥经济技术开发区控股集团有限公司</t>
+          <t>十堰城鑫产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.88</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -15051,17 +15051,17 @@
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>3.0</v>
+        <v>4.45</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -15072,20 +15072,24 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>湖北省-十堰市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还公司债券本金。[23柯控01]</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟将8.25亿元偿还有息债务。</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD64" s="3"/>
+          <t>长江证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr">
+        <is>
+          <t>江西省信用融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE64" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -15098,12 +15102,12 @@
       </c>
       <c r="AG64" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>绍兴柯桥经济技术开发区控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>十堰城鑫产业投资集团有限公司2026年面向专业投资者非公开公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -15119,12 +15123,12 @@
       <c r="AK64" s="3"/>
       <c r="AL64" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t/>
         </is>
       </c>
       <c r="AM64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AN64" s="3" t="inlineStr">
@@ -15134,32 +15138,28 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP64" s="3"/>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="AV64" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW64" s="3" t="inlineStr">
